--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Balance_Desc and Balance_LvUp take the place of QoL_Desc and QoL_LvUp for that entry; an empty cell keeps the QoL text.</t>
+          <t>Balance_Desc and Balance_LvUp take the place of the text generated for the variant; an empty cell keeps the generated text.</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,6 +763,351 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0187.bin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Heal an ally's HP and cure poison.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Heals RES: 4x (+1x/Lv) -&gt; 13x (L10 Max)   |   Heal Cap: 100 (+60-80/Lv) -&gt; 800
+Cures: Poison -&gt; + Paralysis (Lv6+) | TP Cost: 2 (+1-3/Lv) -&gt; 19 | Speed: 1.75x</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Row H036: effect 106 added, value 1 at levels 1 - 5 and 2 at 6 - 10: the first entries of the cure list, poison then paralysis (FORMULAS 16.7, cures). TP: the C rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0188.bin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Circle Heal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Heal the party's HP and cure poison.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Heals RES: 5x -&gt; 5.25 -&gt; 5.5 -&gt; 5.75 -&gt; 6 -&gt; 6.25 -&gt; 6.5 -&gt; 6.75 -&gt; 7 -&gt; 7x (L10)
+Heal Cap: 200 (+40-60/Lv) -&gt; 600   |   TP Cost: 11 (+3-5/Lv) -&gt; 48   |   Speed: 1.35x</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Row H037: effect 106 added, value 1 at every level: poison. The second box is the generated one</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0043.bin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spiral Arrow</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bow/gun skill. Tremendous single shot at an enemy for stab damage.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Row W036: weapon codes 8 and 15, worded as Chain Spike is</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0050.bin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Divine Cannon</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bow/gun skill. Severe stab damage to an enemy, piercing the back row.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Row W037: weapon codes 8 and 15, worded as Chain Spike is</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0038.bin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Short-range/projectile. Severe damage to an enemy. Sleep (20-50%).</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Row S037: weapon codes 0 and 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0039.bin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Silence Sting</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Short-range/projectile. Severe damage to an enemy. Silence (20-50%).</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Row S038: weapon codes 0 and 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0040.bin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Stun Sting</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Short-range/projectile. Severe damage to an enemy. Stun (20-50%).</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Row S039: weapon codes 0 and 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0051.bin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Short-range/projectile. Minor damage and lower speed, enemy row.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Row S040: weapon codes 0 and 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0015.bin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Soul Drain</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ATK: 125% -&gt; 130 -&gt; 135 -&gt; 140 -&gt; 144 -&gt; 148 -&gt; 151 -&gt; 154 -&gt; 157 -&gt; 160% (L10)
+TP Absorb: 10% (+1-2%/Lv) -&gt; 20%   |   TP Cost: 6 -&gt; 18   |   Speed: 0.9x</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rows C152, X046: Speed had no room</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0164.bin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Soul Absorb</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pwr: 55 (+10-20/Lv) -&gt; 205   |   Accuracy: 80% -&gt; 90%   |   TP Absorb: 100%
+TP Cost: 6 (+1/Lv) -&gt; 15   |   Speed: 1.75x   |   Chant: 1.25x -&gt; 1.07x</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Row X026: Speed and Chant had no room</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0200.bin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Illusion</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Create magical afterimages that each let you dodge an attack.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Number of dodges: 3 -&gt; 4 -&gt; 5 (L1-3 Max)   |   Turns: 3 -&gt; 4 -&gt; 5
+TP Cost: 30 -&gt; 38 -&gt; 46   |   Speed: 0.85x   |   Chant: 0.75x -&gt; 0.65x</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Row X071: the sentence of the game says 2 afterimages; the variant gives 3, 4 and 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0216.bin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Shadow Clone</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Number of dodges: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)   |   Chant: 0.75x
+Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 33   |   Speed: 0.85x</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rows K001: the generated box fell back to "Number of dodges UP"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,6 +1108,25 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UniqueSkillData_0379.bin</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Occasionally reflects a percentage of damage taken as fixed damage.
+Reflected: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100%   |   Crown EX: 200%
+Activation rate: 25%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,25 +1108,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>UniqueSkillData_0379.bin</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Occasionally reflects a percentage of damage taken as fixed damage.
-Reflected: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100%   |   Crown EX: 200%
-Activation rate: 25%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Every figure against the built packs by the build (tools/text_checks.py); a doll skill against the action skill its doll performs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Balance_Name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The name the variant gives a skill whose effect it changes; empty keeps the name of the game.</t>
         </is>
       </c>
     </row>
@@ -476,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +522,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Balance_Name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1105,6 +1122,39 @@
       <c r="F22" t="inlineStr">
         <is>
           <t>Rows K001: the generated box fell back to "Number of dodges UP"</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UniqueSkillData_0370.bin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Usurper of Souls</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Enemy attacks and spells are less likely to hit her.
+Evasion: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26%   |   Crown EX: 35%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rows U011 - U020, U051: the skill is evasion in the variant, with a name and a sentence of its own</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Small Target</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,33 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PassiveSkillData_0281.bin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Concentrate</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Interruption rate: -9% -&gt; -17% -&gt; -23% -&gt; -29% -&gt; -33% (L1-5 Max)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Row X14 of the sheet ExePatches: the rate is divided by 1 + value (0.1 to 0.5), which takes off 1 - 1 / (1 + value) of it</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -1144,7 +1144,7 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>Enemy attacks and spells are less likely to hit her.
-Evasion: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26%   |   Crown EX: 35%</t>
+Evasion: 4% -&gt; 6 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26%   |   Crown EX: 35%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -1143,18 +1143,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Enemy attacks and spells are less likely to hit her.
-Evasion: 4% -&gt; 6 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26%   |   Crown EX: 35%</t>
+          <t>When a hit would fell her, she may hold on with 1 HP.
+Activation rate: 15% -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40%   |   Crown EX: 55%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rows U011 - U020, U051: the skill is evasion in the variant, with a name and a sentence of its own</t>
+          <t>Rows U011 - U020, U051: in the variant the skill is the chance to hold on with 1 HP, with a name and a sentence of its own</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Small Target</t>
+          <t>No Miracles Needed</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -1144,7 +1144,7 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>When a hit would fell her, she may hold on with 1 HP.
-Activation rate: 15% -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40%   |   Crown EX: 55%</t>
+Activation rate: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26%   |   Crown EX: 35%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>When a hit would fell her, she may hold on with 1 HP.
+          <t>When a hit would fell her, she may hold on with 1 HP, unless she is at 1 HP already.
 Activation rate: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26%   |   Crown EX: 35%</t>
         </is>
       </c>

--- a/mod_project/data_tables/balance_skill_text.xlsx
+++ b/mod_project/data_tables/balance_skill_text.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>When a hit would fell her, she may hold on with 1 HP, unless she is at 1 HP already.
+          <t>When a hit would fell her, she may hold on with 1 HP.
 Activation rate: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26%   |   Crown EX: 35%</t>
         </is>
       </c>
